--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -127,7 +127,7 @@
     <t>강릉 사업소 현장 점검</t>
   </si>
   <si>
-    <t>강릉 사업소</t>
+    <t>본부 대강당</t>
   </si>
   <si>
     <t>11월 월간 업무계획 보고</t>

--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -124,7 +124,7 @@
     <t>11:00</t>
   </si>
   <si>
-    <t>강릉 사업소 현장 점검</t>
+    <t>본부 실적점검</t>
   </si>
   <si>
     <t>본부 대강당</t>

--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="66">
   <si>
     <t>날짜</t>
   </si>
@@ -863,6 +863,9 @@
       <c r="D16" t="s">
         <v>11</v>
       </c>
+      <c r="E16" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1">

--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="66">
   <si>
     <t>날짜</t>
   </si>
@@ -874,6 +874,9 @@
       <c r="B17" t="s">
         <v>37</v>
       </c>
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
       <c r="D17" t="s">
         <v>7</v>
       </c>

--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -88,7 +88,7 @@
     <t>부본부장</t>
   </si>
   <si>
-    <t>원주 사업소</t>
+    <t>원주지사</t>
   </si>
   <si>
     <t>청렴 교육</t>

--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -85,7 +85,7 @@
     <t>10:30</t>
   </si>
   <si>
-    <t>부본부장</t>
+    <t>국유부장</t>
   </si>
   <si>
     <t>원주지사</t>

--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -79,7 +79,7 @@
     <t>2층 소회의실</t>
   </si>
   <si>
-    <t>원주 사업소 현장 방문</t>
+    <t>원주지사 현장 방문</t>
   </si>
   <si>
     <t>10:30</t>

--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -190,7 +190,7 @@
     <t>개인정보 보호 교육</t>
   </si>
   <si>
-    <t>강릉 사업소 업무 보고</t>
+    <t>국유부문 업무 보고</t>
   </si>
   <si>
     <t>연말 행사 준비 회의</t>

--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -148,7 +148,7 @@
     <t>사업계획 초안 검토</t>
   </si>
   <si>
-    <t>원주 사업소 업무 보고</t>
+    <t>원주지사 업무 보고</t>
   </si>
   <si>
     <t>본사 정책 설명회</t>

--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="65">
   <si>
     <t>날짜</t>
   </si>
@@ -107,9 +107,6 @@
   </si>
   <si>
     <t>고객 만족도 조사 결과 공유</t>
-  </si>
-  <si>
-    <t>사업팀</t>
   </si>
   <si>
     <t>춘천시청 협력사업 협의</t>
@@ -827,7 +824,7 @@
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E14" t="s">
         <v>21</v>
@@ -838,7 +835,7 @@
         <v>46324</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
         <v>19</v>
@@ -847,7 +844,7 @@
         <v>7</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -855,10 +852,10 @@
         <v>46325</v>
       </c>
       <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
         <v>35</v>
-      </c>
-      <c r="C16" t="s">
-        <v>36</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
@@ -872,7 +869,7 @@
         <v>46325</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
@@ -881,7 +878,7 @@
         <v>7</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -906,7 +903,7 @@
         <v>46328</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
         <v>23</v>
@@ -923,10 +920,10 @@
         <v>46329</v>
       </c>
       <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" t="s">
         <v>40</v>
-      </c>
-      <c r="C20" t="s">
-        <v>41</v>
       </c>
       <c r="D20" t="s">
         <v>20</v>
@@ -940,7 +937,7 @@
         <v>46329</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
@@ -951,7 +948,7 @@
         <v>46330</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
@@ -968,13 +965,13 @@
         <v>46330</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
         <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E23" t="s">
         <v>21</v>
@@ -985,7 +982,7 @@
         <v>46331</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
         <v>6</v>
@@ -1002,7 +999,7 @@
         <v>46331</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
         <v>19</v>
@@ -1011,7 +1008,7 @@
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1019,16 +1016,16 @@
         <v>46332</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D26" t="s">
         <v>17</v>
       </c>
       <c r="E26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1036,13 +1033,13 @@
         <v>46332</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1050,10 +1047,10 @@
         <v>46332</v>
       </c>
       <c r="B28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" t="s">
         <v>51</v>
-      </c>
-      <c r="C28" t="s">
-        <v>52</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
@@ -1064,7 +1061,7 @@
         <v>46333</v>
       </c>
       <c r="B29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C29" t="s">
         <v>10</v>
@@ -1073,7 +1070,7 @@
         <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1098,7 +1095,7 @@
         <v>46337</v>
       </c>
       <c r="B31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C31" t="s">
         <v>29</v>
@@ -1112,7 +1109,7 @@
         <v>46338</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C32" t="s">
         <v>6</v>
@@ -1121,7 +1118,7 @@
         <v>7</v>
       </c>
       <c r="E32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1129,7 +1126,7 @@
         <v>46339</v>
       </c>
       <c r="B33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C33" t="s">
         <v>19</v>
@@ -1163,7 +1160,7 @@
         <v>46344</v>
       </c>
       <c r="B35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C35" t="s">
         <v>6</v>
@@ -1172,7 +1169,7 @@
         <v>24</v>
       </c>
       <c r="E35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1180,7 +1177,7 @@
         <v>46345</v>
       </c>
       <c r="B36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
@@ -1197,10 +1194,10 @@
         <v>46346</v>
       </c>
       <c r="B37" t="s">
+        <v>60</v>
+      </c>
+      <c r="C37" t="s">
         <v>61</v>
-      </c>
-      <c r="C37" t="s">
-        <v>62</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -1231,13 +1228,13 @@
         <v>46351</v>
       </c>
       <c r="B39" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D39" t="s">
         <v>20</v>
       </c>
       <c r="E39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1245,7 +1242,7 @@
         <v>46353</v>
       </c>
       <c r="B40" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C40" t="s">
         <v>19</v>
@@ -1279,7 +1276,7 @@
         <v>46358</v>
       </c>
       <c r="B42" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C42" t="s">
         <v>6</v>

--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="64">
   <si>
     <t>날짜</t>
   </si>
@@ -71,9 +71,6 @@
   </si>
   <si>
     <t>15:00</t>
-  </si>
-  <si>
-    <t>경영지원팀</t>
   </si>
   <si>
     <t>2층 소회의실</t>
@@ -708,10 +705,10 @@
         <v>19</v>
       </c>
       <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
         <v>20</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -719,16 +716,16 @@
         <v>46310</v>
       </c>
       <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
         <v>22</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>23</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>24</v>
-      </c>
-      <c r="E8" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -753,10 +750,10 @@
         <v>46316</v>
       </c>
       <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
         <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -770,10 +767,10 @@
         <v>46318</v>
       </c>
       <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
         <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -801,7 +798,7 @@
         <v>46322</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
         <v>6</v>
@@ -818,7 +815,7 @@
         <v>46323</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
@@ -827,7 +824,7 @@
         <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -835,7 +832,7 @@
         <v>46324</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
         <v>19</v>
@@ -844,7 +841,7 @@
         <v>7</v>
       </c>
       <c r="E15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -852,16 +849,16 @@
         <v>46325</v>
       </c>
       <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
         <v>34</v>
       </c>
-      <c r="C16" t="s">
-        <v>35</v>
-      </c>
       <c r="D16" t="s">
         <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -869,7 +866,7 @@
         <v>46325</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
@@ -878,7 +875,7 @@
         <v>7</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -903,10 +900,10 @@
         <v>46328</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -920,16 +917,16 @@
         <v>46329</v>
       </c>
       <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
         <v>39</v>
       </c>
-      <c r="C20" t="s">
-        <v>40</v>
-      </c>
       <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
         <v>20</v>
-      </c>
-      <c r="E20" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -937,7 +934,7 @@
         <v>46329</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
@@ -948,7 +945,7 @@
         <v>46330</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
@@ -965,16 +962,16 @@
         <v>46330</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -982,16 +979,16 @@
         <v>46331</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
         <v>6</v>
       </c>
       <c r="D24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" t="s">
         <v>24</v>
-      </c>
-      <c r="E24" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -999,7 +996,7 @@
         <v>46331</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>19</v>
@@ -1008,7 +1005,7 @@
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1016,16 +1013,16 @@
         <v>46332</v>
       </c>
       <c r="B26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D26" t="s">
         <v>17</v>
       </c>
       <c r="E26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1033,7 +1030,7 @@
         <v>46332</v>
       </c>
       <c r="B27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
@@ -1047,10 +1044,10 @@
         <v>46332</v>
       </c>
       <c r="B28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" t="s">
         <v>50</v>
-      </c>
-      <c r="C28" t="s">
-        <v>51</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
@@ -1061,7 +1058,7 @@
         <v>46333</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C29" t="s">
         <v>10</v>
@@ -1070,7 +1067,7 @@
         <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1095,13 +1092,13 @@
         <v>46337</v>
       </c>
       <c r="B31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D31" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1109,7 +1106,7 @@
         <v>46338</v>
       </c>
       <c r="B32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C32" t="s">
         <v>6</v>
@@ -1118,7 +1115,7 @@
         <v>7</v>
       </c>
       <c r="E32" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1126,7 +1123,7 @@
         <v>46339</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C33" t="s">
         <v>19</v>
@@ -1160,16 +1157,16 @@
         <v>46344</v>
       </c>
       <c r="B35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C35" t="s">
         <v>6</v>
       </c>
       <c r="D35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1177,7 +1174,7 @@
         <v>46345</v>
       </c>
       <c r="B36" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
@@ -1186,7 +1183,7 @@
         <v>11</v>
       </c>
       <c r="E36" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1194,10 +1191,10 @@
         <v>46346</v>
       </c>
       <c r="B37" t="s">
+        <v>59</v>
+      </c>
+      <c r="C37" t="s">
         <v>60</v>
-      </c>
-      <c r="C37" t="s">
-        <v>61</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -1228,13 +1225,13 @@
         <v>46351</v>
       </c>
       <c r="B39" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D39" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1242,7 +1239,7 @@
         <v>46353</v>
       </c>
       <c r="B40" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C40" t="s">
         <v>19</v>
@@ -1276,7 +1273,7 @@
         <v>46358</v>
       </c>
       <c r="B42" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C42" t="s">
         <v>6</v>
